--- a/mahkeme/2025-02-Dosya Listesi222.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi222.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C5E22B-92B6-47E1-9648-308CA2085B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74556E-C3A5-449D-B1EF-784B5D356FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,26 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>Dosya Listesi</t>
   </si>
   <si>
-    <t>Alacaklı</t>
-  </si>
-  <si>
-    <t>Tokat İcra Dairesi</t>
-  </si>
-  <si>
     <t>2025/1266</t>
   </si>
   <si>
-    <t>İcra Dosyası</t>
-  </si>
-  <si>
-    <t>Açık</t>
-  </si>
-  <si>
     <t>2024/22182</t>
   </si>
   <si>
@@ -67,9 +55,6 @@
     <t>2024/3369</t>
   </si>
   <si>
-    <t>2023/20377</t>
-  </si>
-  <si>
     <t>salihant</t>
   </si>
   <si>
@@ -88,9 +73,6 @@
     <t>alidemirel</t>
   </si>
   <si>
-    <t>ö14-xxx</t>
-  </si>
-  <si>
     <t>2024/217</t>
   </si>
   <si>
@@ -100,9 +82,6 @@
     <t>red</t>
   </si>
   <si>
-    <t>kabul</t>
-  </si>
-  <si>
     <t>icr-ö13</t>
   </si>
   <si>
@@ -125,29 +104,38 @@
   </si>
   <si>
     <t>KBL</t>
+  </si>
+  <si>
+    <t>TL</t>
+  </si>
+  <si>
+    <t>Dosya No</t>
+  </si>
+  <si>
+    <t>Açlş</t>
+  </si>
+  <si>
+    <t>Karar</t>
+  </si>
+  <si>
+    <t>icr-thly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7" tint="0.79998168889431442"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -183,8 +171,31 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="7" tint="0.79998168889431442"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,8 +232,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -230,33 +259,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,422 +622,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="7" width="8.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="6" max="7" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="21">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6">
+        <v>45588</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="17">
+        <v>178</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="19">
+        <v>45604</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3">
+        <v>214</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19">
+        <v>45676</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3">
+        <v>113</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6">
+        <v>45588</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="18">
+        <v>198</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19">
+        <v>45603</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <v>45676</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="5">
+        <v>45537</v>
+      </c>
+      <c r="G12" s="5">
+        <v>45691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5">
+        <v>45438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F15" s="29">
+        <v>45486</v>
+      </c>
+      <c r="G15" s="10">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="6">
-        <v>178</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10">
-        <v>45604</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="E16" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="5">
-        <v>198</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>45603</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10">
-        <v>45588</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10">
-        <v>45588</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5">
-        <v>97</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5">
-        <v>214</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5">
-        <v>113</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="9">
-        <v>45342</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="9">
-        <v>45691</v>
-      </c>
-      <c r="G12" s="9">
-        <v>45537</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="9">
-        <v>45438</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="28">
+        <v>45590</v>
+      </c>
+      <c r="G16" s="28">
+        <v>45688</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="17">
-        <v>45588</v>
-      </c>
-      <c r="G16" s="9">
-        <v>45486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="14">
-        <v>45688</v>
-      </c>
-      <c r="G17" s="9">
-        <v>45590</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9">
-        <v>45288</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K19" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
